--- a/artfynd/A 974-2023 artfynd.xlsx
+++ b/artfynd/A 974-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 974-2023 artfynd.xlsx
+++ b/artfynd/A 974-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3784070</v>
+        <v>701354</v>
       </c>
       <c r="B2" t="n">
-        <v>103345</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221423</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589292.9704679282</v>
+        <v>589284</v>
       </c>
       <c r="R2" t="n">
-        <v>6412496.696579667</v>
+        <v>6412633</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,26 +743,11 @@
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>måttligt</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,7 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>lövsnår</t>
+          <t>ljus lövskog vid nordvänd häll</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # 140 cm grov ek</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2379668</v>
+        <v>724372</v>
       </c>
       <c r="B3" t="n">
-        <v>76906</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6436</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589278.3300888247</v>
+        <v>589278</v>
       </c>
       <c r="R3" t="n">
-        <v>6412627.349320733</v>
+        <v>6412637</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,26 +853,11 @@
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>rikligt på 1 träd</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -904,9 +872,12 @@
           <t>ljus lövskog vid nordvänd häll</t>
         </is>
       </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>140 cm grov ek</t>
+          <t>1 substratenheter # 140 cm grov ek</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>701354</v>
+        <v>2379668</v>
       </c>
       <c r="B4" t="n">
-        <v>93131</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>6436</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589283.5435439356</v>
+        <v>589278</v>
       </c>
       <c r="R4" t="n">
-        <v>6412632.789444264</v>
+        <v>6412627</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,19 +963,14 @@
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>rikligt på 1 träd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,12 +987,9 @@
           <t>ljus lövskog vid nordvänd häll</t>
         </is>
       </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # 140 cm grov ek</t>
+          <t>140 cm grov ek</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1049,53 +1007,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>724372</v>
+        <v>107306227</v>
       </c>
       <c r="B5" t="n">
-        <v>92938</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2779</v>
+        <v>101479</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Osmoderma eremita</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vistingsö, Sm</t>
+          <t>Värmvik, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589278.1053252611</v>
+        <v>589291</v>
       </c>
       <c r="R5" t="n">
-        <v>6412637.460350129</v>
+        <v>6412639</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1078,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2006-09-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2006-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillning vid en ek, ett särskilt skyddsvärt träd, trädet är dött och har stor hålighet med mulm.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,29 +1099,16 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>ljus lövskog vid nordvänd häll</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter # 140 cm grov ek</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Anna von Wirth</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Anna von Wirth</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1177,12 +1118,7 @@
         <v>13223544</v>
       </c>
       <c r="B6" t="n">
-        <v>29896</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>30288</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589273.4132154997</v>
+        <v>589273</v>
       </c>
       <c r="R6" t="n">
-        <v>6412632.564251013</v>
+        <v>6412633</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,19 +1183,9 @@
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2006-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1296,59 +1222,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107306227</v>
+        <v>3784070</v>
       </c>
       <c r="B7" t="n">
-        <v>9491</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101479</v>
+        <v>221423</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Osmoderma eremita</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Värmvik, Sm</t>
+          <t>Vistingsö, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589291.4110257613</v>
+        <v>589293</v>
       </c>
       <c r="R7" t="n">
-        <v>6412638.820995423</v>
+        <v>6412497</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,27 +1287,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-09-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-09-29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spillning vid en ek, ett särskilt skyddsvärt träd, trädet är dött och har stor hålighet med mulm.</t>
+          <t>måttligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,16 +1308,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>lövsnår</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna von Wirth</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna von Wirth</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
